--- a/education_surveys/034_educational_content_creator_survey--education_surveys.xlsx
+++ b/education_surveys/034_educational_content_creator_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,64 +520,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>What's your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>experience_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>How long have you been creating educational content?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>What type of content do you typically create?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>What motivates you to create educational content?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,87 +612,87 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>tool_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Can you describe your experience with content creation tools?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>share_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>How do you typically share your content with others?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_description_2</t>
+          <t>favorite_tools</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_description_2</t>
+          <t>What are your favorite tools for content creation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool_2</t>
+          <t>effectiveness_measure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_tool_2</t>
+          <t>How do you measure the effectiveness of your content?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>content_creation_process</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Can you walk us through your content creation process?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_file_name</t>
+          <t>tools_used</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form_file_name</t>
+          <t>Have you used any of the following tools for content creation?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_file_name</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>form_file_name</t>
+          <t>Have you created content for any of the following types of clients?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_file_name_2</t>
+          <t>satisfaction_level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>form_file_name_2</t>
+          <t>On a scale of 1-10, how satisfied are you with your current content creation workflow?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,34 +827,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'education_surveys'}</t>
+          <t>educational_videos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Education Surveys'}</t>
+          <t>Educational Videos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'other'}</t>
+          <t>educational_podcasts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Other'}</t>
+          <t>Educational Podcasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>content_type_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>educational_blogs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Educational Blogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>content_type_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>educational_courses</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Educational Courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>content_type_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>share_method_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>share_method_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>share_method_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>share_method_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>favorite_tools_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>google_slides</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Google Slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>favorite_tools_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>powerpoint</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>favorite_tools_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>canva</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>favorite_tools_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>adobe_creative_cloud</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Adobe Creative Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>favorite_tools_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>effectiveness_measure_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>effectiveness_measure_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>completion_rate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Completion Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>effectiveness_measure_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Satisfaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effectiveness_measure_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tools_used_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>google_slides</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Google Slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tools_used_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>powerpoint</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tools_used_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>canva</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tools_used_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>adobe_creative_cloud</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Adobe Creative Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tools_used_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>clients_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>schools</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>clients_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>clients_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>non-profit</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>clients_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>personal_projects</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Personal projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>clients_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
